--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="301">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,6 +484,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -673,6 +676,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -683,10 +689,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -699,6 +720,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -706,6 +736,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -713,6 +746,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -866,6 +902,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1242,7 +1284,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3663,7 +3705,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3734,10 +3778,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3771,7 +3815,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3793,7 +3837,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3811,7 +3855,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3831,10 +3875,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3868,7 +3912,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3890,7 +3934,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3908,7 +3952,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3928,10 +3972,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3945,7 +3989,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -3957,10 +4001,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4011,7 +4055,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4031,10 +4075,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4048,7 +4092,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4057,13 +4101,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4114,7 +4158,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4134,10 +4178,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4235,10 +4279,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4254,7 +4298,7 @@
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4267,7 +4311,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4279,7 +4323,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4318,7 +4362,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4338,17 +4382,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4357,7 +4401,7 @@
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4370,7 +4414,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4382,7 +4426,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4421,7 +4465,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4441,17 +4485,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4473,7 +4517,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4485,7 +4529,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4524,7 +4568,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4544,17 +4588,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4576,7 +4620,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4627,7 +4671,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4647,17 +4691,17 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -4666,7 +4710,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4679,7 +4723,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4691,7 +4735,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4730,7 +4774,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4750,10 +4794,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4776,11 +4820,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4831,7 +4875,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4851,10 +4895,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4881,7 +4925,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4932,7 +4976,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4952,17 +4996,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4980,11 +5024,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5035,7 +5079,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5055,17 +5099,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5083,11 +5127,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5138,7 +5182,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5158,17 +5202,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5186,11 +5230,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5241,7 +5285,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5261,10 +5305,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5278,7 +5322,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5287,16 +5331,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5344,7 +5390,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5364,10 +5410,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5381,7 +5427,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5390,15 +5436,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5447,7 +5495,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5467,10 +5515,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5493,12 +5541,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5546,7 +5598,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5566,10 +5618,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5594,10 +5646,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5625,7 +5681,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5643,7 +5699,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5663,10 +5719,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5689,12 +5745,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -5742,7 +5804,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5762,10 +5824,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5788,12 +5850,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5841,7 +5905,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5861,10 +5925,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5887,12 +5951,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5940,7 +6006,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5960,10 +6026,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5977,7 +6043,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -5986,10 +6052,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6041,7 +6107,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6061,10 +6127,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6162,10 +6228,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6263,10 +6329,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6364,10 +6430,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6465,10 +6531,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6568,10 +6634,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6671,10 +6737,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6774,10 +6840,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6877,10 +6943,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6978,10 +7044,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7011,7 +7077,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
@@ -7037,7 +7103,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7055,7 +7121,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7075,10 +7141,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7112,7 +7178,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>74</v>
@@ -7154,7 +7220,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7174,10 +7240,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7200,7 +7266,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7253,7 +7319,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7273,10 +7339,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7299,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7352,7 +7418,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7372,10 +7438,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7398,7 +7464,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7451,7 +7517,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7471,10 +7537,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7497,7 +7563,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7550,7 +7616,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7570,10 +7636,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7596,7 +7662,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7649,7 +7715,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7669,10 +7735,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7695,7 +7761,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7748,7 +7814,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7768,10 +7834,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7794,7 +7860,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7847,7 +7913,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7867,10 +7933,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7893,7 +7959,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7946,7 +8012,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -7966,10 +8032,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7992,7 +8058,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8045,7 +8111,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8065,10 +8131,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8091,12 +8157,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L68" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>74</v>
       </c>
@@ -8144,7 +8214,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8164,10 +8234,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8265,10 +8335,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8366,10 +8436,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8467,10 +8537,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8568,10 +8638,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8671,10 +8741,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8774,10 +8844,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8877,10 +8947,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8980,10 +9050,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9081,10 +9151,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9111,7 +9181,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9120,7 +9190,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>74</v>
@@ -9162,7 +9232,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9182,10 +9252,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9219,7 +9289,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>74</v>
@@ -9261,7 +9331,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9281,10 +9351,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9307,7 +9377,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9360,7 +9430,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitements-administres.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
